--- a/data/trending_integrated_20260914_14.xlsx
+++ b/data/trending_integrated_20260914_14.xlsx
@@ -581,10 +581,10 @@
         <v>171</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>270117694955</v>
+        <v>270347260265</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 언급되며, 3연상 가능성에 대한 기대와 시세 끝을 조심하라는 의견이 공존. 주포 및 프로그램 매수 언급.</t>
+          <t>3연상 가능성 언급과 차세대 광반도체, 광통신 관련주로서의 기대감 표출.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '주포']</t>
+          <t>['광반도체', '광통신', '프로그램']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6520</v>
+        <v>9640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+18.33%</t>
+          <t>+21.87%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.55</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="H3" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5510</v>
+        <v>7910</v>
       </c>
       <c r="K3" t="n">
-        <v>5910</v>
+        <v>7800</v>
       </c>
       <c r="L3" t="n">
-        <v>7160</v>
+        <v>9840</v>
       </c>
       <c r="M3" t="n">
-        <v>5890</v>
+        <v>7540</v>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>52941563310</v>
+        <v>92263517660</v>
       </c>
       <c r="P3" t="n">
-        <v>10360</v>
+        <v>25050</v>
       </c>
       <c r="Q3" t="n">
-        <v>2965</v>
+        <v>3705</v>
       </c>
       <c r="R3" t="n">
-        <v>-63000</v>
+        <v>19000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI 보안', '딥페이크', '단기 급등']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9210</v>
+        <v>6530</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.43%</t>
+          <t>+18.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H4" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7910</v>
+        <v>5510</v>
       </c>
       <c r="K4" t="n">
-        <v>7800</v>
+        <v>5910</v>
       </c>
       <c r="L4" t="n">
-        <v>9840</v>
+        <v>7160</v>
       </c>
       <c r="M4" t="n">
-        <v>7540</v>
+        <v>5890</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>78985955980</v>
+        <v>53197624465</v>
       </c>
       <c r="P4" t="n">
-        <v>25050</v>
+        <v>10360</v>
       </c>
       <c r="Q4" t="n">
-        <v>3705</v>
+        <v>2965</v>
       </c>
       <c r="R4" t="n">
-        <v>19000</v>
+        <v>-63000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['AI 보안', '딥페이크', '단기 급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2920</v>
+        <v>2910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+12.96%</t>
+          <t>+12.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>37790780570</v>
+        <v>38294457885</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4260</v>
+        <v>9180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.08%</t>
+          <t>+10.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.45</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="H6" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3870</v>
+        <v>8290</v>
       </c>
       <c r="K6" t="n">
-        <v>3860</v>
+        <v>8300</v>
       </c>
       <c r="L6" t="n">
-        <v>4620</v>
+        <v>9440</v>
       </c>
       <c r="M6" t="n">
-        <v>3740</v>
+        <v>8300</v>
       </c>
       <c r="N6" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>284902384919</v>
+        <v>43263480210</v>
       </c>
       <c r="P6" t="n">
-        <v>8100</v>
+        <v>12800</v>
       </c>
       <c r="Q6" t="n">
-        <v>592</v>
+        <v>5340</v>
       </c>
       <c r="R6" t="n">
-        <v>-161000</v>
+        <v>507000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6G 시대 및 AIDC 광통신 기술과 연관되어 상한가 가능성 언급. 국책 사업 선정 및 기술력에 대한 긍정적 전망 제시. 투자 경고 종목으로 지정된 상태.</t>
+          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['6G', '광통신', '국책사업']</t>
+          <t>['폴더블', '매출 증', '전환사채']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>441270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9090</v>
+        <v>4250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.65%</t>
+          <t>+9.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.45</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="G7" t="n">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8290</v>
+        <v>3870</v>
       </c>
       <c r="K7" t="n">
-        <v>8300</v>
+        <v>3860</v>
       </c>
       <c r="L7" t="n">
-        <v>9440</v>
+        <v>4620</v>
       </c>
       <c r="M7" t="n">
-        <v>8300</v>
+        <v>3740</v>
       </c>
       <c r="N7" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="O7" t="n">
-        <v>42896934930</v>
+        <v>289460252388</v>
       </c>
       <c r="P7" t="n">
-        <v>12800</v>
+        <v>8100</v>
       </c>
       <c r="Q7" t="n">
-        <v>5340</v>
+        <v>592</v>
       </c>
       <c r="R7" t="n">
-        <v>507000</v>
+        <v>-161000</v>
       </c>
       <c r="S7" t="n">
-        <v>109000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
+          <t>6G 시대 개막 및 AIDC 광통신 기술 부각, 국책사업 선정 가능성을 근거로 한 강한 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['폴더블', '매출 증', '전환사채']</t>
+          <t>['6G', 'AIDC', '광통신']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2800</v>
+        <v>2805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.87%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H8" t="n">
         <v>1.44</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>100474607708</v>
+        <v>100881090773</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17000</v>
+        <v>16900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.85%</t>
+          <t>+5.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>258806924450</v>
+        <v>260512814680</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 및 트럼프 발언에 따른 변동성 발생. 보안주로서 남은 가치 언급 및 지지선 이탈 가능성 시사.</t>
+          <t>AI 개발 속도 조절론 급부상 속에서 보안주로서의 부각 가능성 언급 및 투자자들의 혼재된 심리.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '지지선']</t>
+          <t>['AI', '보안주', '속도조절론']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>70417875050</v>
+        <v>73973452725</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14480</v>
+        <v>8530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.33%</t>
+          <t>+2.90%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="F11" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G11" t="n">
-        <v>680</v>
+        <v>1367</v>
       </c>
       <c r="H11" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14150</v>
+        <v>8290</v>
       </c>
       <c r="K11" t="n">
-        <v>13850</v>
+        <v>8100</v>
       </c>
       <c r="L11" t="n">
-        <v>14950</v>
+        <v>9050</v>
       </c>
       <c r="M11" t="n">
-        <v>13800</v>
+        <v>8060</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>163402643530</v>
+        <v>31624272790</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>21500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>-407000</v>
+        <v>-43000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 성장과 함께 대장주로서의 상승 가능성 언급. 광전자 사려다 잘못 산 종목이라는 의견도 존재. 프로그램 매수세 유입.</t>
+          <t>암 치료 바이오 신약 관련 임상 결과 발표 및 글로벌 심포지엄 개최를 바탕으로 한 핵폭탄급 재료 및 높은 상승 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '대장주', '기술력']</t>
+          <t>['항암', '신약', '심포지엄']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8410</v>
+        <v>14420</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="F12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G12" t="n">
-        <v>1317</v>
+        <v>704</v>
       </c>
       <c r="H12" t="n">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8290</v>
+        <v>14150</v>
       </c>
       <c r="K12" t="n">
-        <v>8100</v>
+        <v>13850</v>
       </c>
       <c r="L12" t="n">
-        <v>9050</v>
+        <v>14950</v>
       </c>
       <c r="M12" t="n">
-        <v>8060</v>
+        <v>13800</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>31380842835</v>
+        <v>166007464230</v>
       </c>
       <c r="P12" t="n">
-        <v>21500</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-43000</v>
+        <v>-407000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 개발 관련 재료가 핵폭탄급이며, 글로벌 제약사 멘토의 임상 결과 발표에 대한 기대감이 높음. 시총이 낮아 목표가 30만 원 이상 제시.</t>
+          <t>GPU 확보 다음 단계인 '연결' 및 AIDC 광통신 기술 부각, 광통신 중 대장주로서의 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['항암제', '임상', '신약']</t>
+          <t>['GPU', 'AIDC', '광통신']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14620</v>
+        <v>14680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F13" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G13" t="n">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>107344184675</v>
+        <v>107652973105</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>16095506408</v>
+        <v>16187431690</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87800</v>
+        <v>250000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.30%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>233</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>132</v>
+        <v>479</v>
       </c>
       <c r="G15" t="n">
-        <v>775</v>
+        <v>1780</v>
       </c>
       <c r="H15" t="n">
-        <v>23.56</v>
+        <v>46.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>90800</v>
+        <v>259500</v>
       </c>
       <c r="K15" t="n">
-        <v>89800</v>
+        <v>249500</v>
       </c>
       <c r="L15" t="n">
-        <v>90400</v>
+        <v>254500</v>
       </c>
       <c r="M15" t="n">
-        <v>87700</v>
+        <v>249000</v>
       </c>
       <c r="N15" t="n">
-        <v>23.59</v>
+        <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>175806863500</v>
+        <v>3041532365250</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>-546000</v>
+        <v>-2691000</v>
       </c>
       <c r="S15" t="n">
-        <v>-91000</v>
+        <v>-1229000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>원전주 상승 가능성 언급. 국제 유가 상승 및 한미 정부 지원에 따른 구조적 상승 기대. 공매도 평단가 언급.</t>
+          <t>AI 속도 조절론, 정치적 이슈와 연계된 부정적 전망 및 투자자 불만 토로.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '국제유가', '공매도']</t>
+          <t>['AI', '금산법', '실적']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>250500</v>
+        <v>87300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.47%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>238</v>
       </c>
       <c r="F16" t="n">
-        <v>478</v>
+        <v>134</v>
       </c>
       <c r="G16" t="n">
-        <v>1773</v>
+        <v>795</v>
       </c>
       <c r="H16" t="n">
-        <v>46.64</v>
+        <v>23.56</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>259500</v>
+        <v>90800</v>
       </c>
       <c r="K16" t="n">
-        <v>249500</v>
+        <v>89800</v>
       </c>
       <c r="L16" t="n">
-        <v>254500</v>
+        <v>90400</v>
       </c>
       <c r="M16" t="n">
-        <v>249000</v>
+        <v>87300</v>
       </c>
       <c r="N16" t="n">
-        <v>46.71</v>
+        <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>2898203555750</v>
+        <v>185127380850</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>75900</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>-2691000</v>
+        <v>-546000</v>
       </c>
       <c r="S16" t="n">
-        <v>-1229000</v>
+        <v>-91000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 속도 조절론, 정치적 이슈와 연관된 부정적 전망이 주를 이룸. 실제 기업 분석보다는 정치적 논쟁이 주로 언급됨.</t>
+          <t>우상향 추세 및 급등 구간 진입 기대감과 함께, 국제 유가 상승 시 원전주 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI', '정치', '개미']</t>
+          <t>['국제유가', '원전주', '공매']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18790</v>
+        <v>11600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-5.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>461</v>
+        <v>102</v>
       </c>
       <c r="H17" t="n">
-        <v>10.55</v>
+        <v>0.22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19890</v>
+        <v>12290</v>
       </c>
       <c r="K17" t="n">
-        <v>19480</v>
+        <v>12030</v>
       </c>
       <c r="L17" t="n">
-        <v>19550</v>
+        <v>13230</v>
       </c>
       <c r="M17" t="n">
-        <v>18700</v>
+        <v>11590</v>
       </c>
       <c r="N17" t="n">
-        <v>10.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>69128939725</v>
+        <v>58002994415</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>20850</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>4020</v>
       </c>
       <c r="R17" t="n">
-        <v>-480000</v>
+        <v>11000</v>
       </c>
       <c r="S17" t="n">
-        <v>-158000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 권유 및 공매도 작살 가능성 언급. 저점이 높아지고 있으며, 침착한 기다림이 필요하다는 의견.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주주운동']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,130 +2028,130 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11610</v>
+        <v>1705000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.72</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>481</v>
       </c>
       <c r="G18" t="n">
-        <v>98</v>
+        <v>1851</v>
       </c>
       <c r="H18" t="n">
-        <v>0.22</v>
+        <v>50.47</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>12290</v>
+        <v>1812000</v>
       </c>
       <c r="K18" t="n">
-        <v>12030</v>
+        <v>1707000</v>
       </c>
       <c r="L18" t="n">
-        <v>13230</v>
+        <v>1740000</v>
       </c>
       <c r="M18" t="n">
-        <v>11590</v>
+        <v>1695000</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9399999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>57766811350</v>
+        <v>4741438821500</v>
       </c>
       <c r="P18" t="n">
-        <v>20850</v>
+        <v>2987000</v>
       </c>
       <c r="Q18" t="n">
-        <v>4020</v>
+        <v>325000</v>
       </c>
       <c r="R18" t="n">
-        <v>11000</v>
+        <v>-1020000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-202000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
+          <t>금리 인상 불확실성 해소 기대와 함께, 외국인 선물 매수 전환 언급에도 불구하고 하락세 및 투자자들의 부정적 심리.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '재료 소멸']</t>
+          <t>['금리', '외인', 'AI']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1707000</v>
+        <v>18680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.79%</t>
+          <t>-6.08%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
-        <v>484</v>
+        <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>1809</v>
+        <v>467</v>
       </c>
       <c r="H19" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K19" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L19" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M19" t="n">
-        <v>1695000</v>
+        <v>18660</v>
       </c>
       <c r="N19" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>4645299685500</v>
+        <v>70945285955</v>
       </c>
       <c r="P19" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-1020000</v>
+        <v>-480000</v>
       </c>
       <c r="S19" t="n">
-        <v>-202000</v>
+        <v>-158000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 금리 인상 불확실성, 국내 정치 상황과 연관된 부정적 전망이 지배적. AI 개발 속도 제한 우려 및 급락 가능성 언급.</t>
+          <t>대차해지 운동 동참 권유 및 공매도 작살 가능성 언급. 저점이 높아지고 있으며, 침착한 기다림이 필요하다는 의견.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['금리', 'AI', '외인']</t>
+          <t>['대차해지', '공매도', '주주운동']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13780</v>
+        <v>13800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.32%</t>
+          <t>-6.19%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>29407834840</v>
+        <v>29561514020</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11360</v>
+        <v>11240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.76%</t>
+          <t>-9.72%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2352,13 +2352,13 @@
         <v>13900</v>
       </c>
       <c r="M21" t="n">
-        <v>11310</v>
+        <v>11240</v>
       </c>
       <c r="N21" t="n">
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>64522356635</v>
+        <v>65162138690</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>

--- a/data/trending_integrated_20260914_14.xlsx
+++ b/data/trending_integrated_20260914_14.xlsx
@@ -578,10 +578,10 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" t="n">
         <v>236</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>270347260265</v>
+        <v>270513367245</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -619,14 +619,14 @@
         <v>1760</v>
       </c>
       <c r="R2" t="n">
-        <v>-15000</v>
+        <v>-16000</v>
       </c>
       <c r="S2" t="n">
         <v>-18000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3연상 가능성 언급과 차세대 광반도체, 광통신 관련주로서의 기대감 표출.</t>
+          <t>광통신 대장주로서의 기대감과 3연상 가능성에 대한 언급. 일부에서는 시세 끝 조심 및 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '프로그램']</t>
+          <t>['광통신', '3연상', '주포']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9640</v>
+        <v>9820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.87%</t>
+          <t>+24.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.55</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -693,7 +693,7 @@
         <v>7800</v>
       </c>
       <c r="L3" t="n">
-        <v>9840</v>
+        <v>9880</v>
       </c>
       <c r="M3" t="n">
         <v>7540</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>92263517660</v>
+        <v>103935841395</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -711,7 +711,7 @@
         <v>3705</v>
       </c>
       <c r="R3" t="n">
-        <v>19000</v>
+        <v>33000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6530</v>
+        <v>6660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.51%</t>
+          <t>+20.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H4" t="n">
         <v>1.67</v>
@@ -794,7 +794,7 @@
         <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>53197624465</v>
+        <v>58591942780</v>
       </c>
       <c r="P4" t="n">
         <v>10360</v>
@@ -803,7 +803,7 @@
         <v>2965</v>
       </c>
       <c r="R4" t="n">
-        <v>-63000</v>
+        <v>-66000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2910</v>
+        <v>2875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+12.57%</t>
+          <t>+11.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>38294457885</v>
+        <v>38577669085</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -895,7 +895,7 @@
         <v>2050</v>
       </c>
       <c r="R5" t="n">
-        <v>109000</v>
+        <v>186000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9180</v>
+        <v>9160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.74%</t>
+          <t>+10.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>43263480210</v>
+        <v>43585131640</v>
       </c>
       <c r="P6" t="n">
         <v>12800</v>
@@ -987,10 +987,10 @@
         <v>5340</v>
       </c>
       <c r="R6" t="n">
-        <v>507000</v>
+        <v>568000</v>
       </c>
       <c r="S6" t="n">
-        <v>109000</v>
+        <v>104000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1038,13 +1038,13 @@
         <v>-0.45</v>
       </c>
       <c r="E7" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F7" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G7" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H7" t="n">
         <v>0.59</v>
@@ -1070,7 +1070,7 @@
         <v>1.04</v>
       </c>
       <c r="O7" t="n">
-        <v>289460252388</v>
+        <v>293646813872</v>
       </c>
       <c r="P7" t="n">
         <v>8100</v>
@@ -1079,23 +1079,23 @@
         <v>592</v>
       </c>
       <c r="R7" t="n">
-        <v>-161000</v>
+        <v>-202000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6G 시대 개막 및 AIDC 광통신 기술 부각, 국책사업 선정 가능성을 근거로 한 강한 상승 기대감 표출.</t>
+          <t>6G 시대 개막 및 국책사업 선정 가능성에 따른 8000원 이상 목표가 제시. 투자 경고 및 변동성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['6G', 'AIDC', '광통신']</t>
+          <t>['6G', '국책사업', '투자경고']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H8" t="n">
         <v>1.44</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>100881090773</v>
+        <v>101821482105</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1171,7 +1171,7 @@
         <v>1400</v>
       </c>
       <c r="R8" t="n">
-        <v>-275000</v>
+        <v>-306000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16900</v>
+        <v>16880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.23%</t>
+          <t>+5.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>260512814680</v>
+        <v>262229708020</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1263,23 +1263,23 @@
         <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-281000</v>
+        <v>-295000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 급부상 속에서 보안주로서의 부각 가능성 언급 및 투자자들의 혼재된 심리.</t>
+          <t>AI 개발 속도 조절론과 보안주로서의 역할에 대한 기대감. 2연상 가능성 언급 및 매도세에 대한 불만 표현.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '속도조절론']</t>
+          <t>['AI', '보안주', '2연상']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,7 +1314,7 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F10" t="n">
         <v>75</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>73973452725</v>
+        <v>77146905175</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1355,14 +1355,14 @@
         <v>18440</v>
       </c>
       <c r="R10" t="n">
-        <v>368000</v>
+        <v>688000</v>
       </c>
       <c r="S10" t="n">
-        <v>36000</v>
+        <v>49000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 수주 성공으로 작년 실적 돌파. 쇄빙선, LNG선 등 신규 수주 기대감과 함께 증권사 목표가 상향 언급. 공매도 감소 및 숏커버 가능성 언급.</t>
+          <t>대형 상선 수주 성공 및 1.6조 원 규모 실적 돌파, 증권사 목표가 상향 등 긍정적 요인에 기반한 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '실적', '공매도']</t>
+          <t>['수주', 'LNG선', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8530</v>
+        <v>8560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.90%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G11" t="n">
-        <v>1367</v>
+        <v>1378</v>
       </c>
       <c r="H11" t="n">
         <v>0.75</v>
@@ -1438,7 +1438,7 @@
         <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>31624272790</v>
+        <v>32004687535</v>
       </c>
       <c r="P11" t="n">
         <v>21500</v>
@@ -1447,19 +1447,19 @@
         <v>2300</v>
       </c>
       <c r="R11" t="n">
-        <v>-43000</v>
+        <v>-27000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 관련 임상 결과 발표 및 글로벌 심포지엄 개최를 바탕으로 한 핵폭탄급 재료 및 높은 상승 기대감.</t>
+          <t>항암 신약 임상 결과 발표 및 글로벌 심포지엄 개최 등 핵폭탄급 재료 기반 상승 기대. 낮은 시가총액으로 인한 큰 폭 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14420</v>
+        <v>15000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.67%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E12" t="n">
-        <v>194</v>
+        <v>299</v>
       </c>
       <c r="F12" t="n">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="G12" t="n">
-        <v>704</v>
+        <v>789</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K12" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>14950</v>
+        <v>16510</v>
       </c>
       <c r="M12" t="n">
-        <v>13800</v>
+        <v>14320</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O12" t="n">
-        <v>166007464230</v>
+        <v>108691448605</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
-        <v>-407000</v>
+        <v>-83000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>GPU 확보 다음 단계인 '연결' 및 AIDC 광통신 기술 부각, 광통신 중 대장주로서의 상승 가능성 언급.</t>
+          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['GPU', 'AIDC', '광통신']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14680</v>
+        <v>14390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.97</v>
+        <v>-0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="F13" t="n">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="G13" t="n">
-        <v>748</v>
+        <v>805</v>
       </c>
       <c r="H13" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14610</v>
+        <v>14150</v>
       </c>
       <c r="K13" t="n">
-        <v>15420</v>
+        <v>13850</v>
       </c>
       <c r="L13" t="n">
-        <v>16510</v>
+        <v>14950</v>
       </c>
       <c r="M13" t="n">
-        <v>14320</v>
+        <v>13800</v>
       </c>
       <c r="N13" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>107652973105</v>
+        <v>168214182280</v>
       </c>
       <c r="P13" t="n">
-        <v>36200</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>8920</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-108000</v>
+        <v>-325000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
+          <t>AIDC 광통신 기술 성장 및 15000원 돌파 기대감. 대장주로서의 역할 수행 미흡에 대한 아쉬움 표현.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['광통신', 'AIDC', '대장주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>16187431690</v>
+        <v>16342265201</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1723,7 +1723,7 @@
         <v>1524</v>
       </c>
       <c r="R14" t="n">
-        <v>-273000</v>
+        <v>-280000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>250000</v>
+        <v>249750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.66%</t>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G15" t="n">
-        <v>1780</v>
+        <v>1769</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3041532365250</v>
+        <v>3132141379750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1815,10 +1815,10 @@
         <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>-2691000</v>
+        <v>-2979000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1229000</v>
+        <v>-1253000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87300</v>
+        <v>86300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F16" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G16" t="n">
-        <v>795</v>
+        <v>828</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1892,13 +1892,13 @@
         <v>90400</v>
       </c>
       <c r="M16" t="n">
-        <v>87300</v>
+        <v>86300</v>
       </c>
       <c r="N16" t="n">
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>185127380850</v>
+        <v>199442286200</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1907,10 +1907,10 @@
         <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>-546000</v>
+        <v>-621000</v>
       </c>
       <c r="S16" t="n">
-        <v>-91000</v>
+        <v>-125000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11600</v>
+        <v>11560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H17" t="n">
         <v>0.22</v>
@@ -1984,13 +1984,13 @@
         <v>13230</v>
       </c>
       <c r="M17" t="n">
-        <v>11590</v>
+        <v>11550</v>
       </c>
       <c r="N17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>58002994415</v>
+        <v>58449553075</v>
       </c>
       <c r="P17" t="n">
         <v>20850</v>
@@ -1999,7 +1999,7 @@
         <v>4020</v>
       </c>
       <c r="R17" t="n">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1705000</v>
+        <v>1701000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-6.13%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="G18" t="n">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4741438821500</v>
+        <v>4873211088000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2091,14 +2091,14 @@
         <v>325000</v>
       </c>
       <c r="R18" t="n">
-        <v>-1020000</v>
+        <v>-1117000</v>
       </c>
       <c r="S18" t="n">
-        <v>-202000</v>
+        <v>-203000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금리 인상 불확실성 해소 기대와 함께, 외국인 선물 매수 전환 언급에도 불구하고 하락세 및 투자자들의 부정적 심리.</t>
+          <t>하락세에 대한 불만과 정치적 언급이 혼재. 연말 300 목표가 및 외국인 선물 매수 전환 등 일부 긍정적 요소 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['금리', '외인', 'AI']</t>
+          <t>['미국금리', '외국인', 'AI']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18680</v>
+        <v>18520</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>-6.89%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H19" t="n">
         <v>10.55</v>
@@ -2168,13 +2168,13 @@
         <v>19550</v>
       </c>
       <c r="M19" t="n">
-        <v>18660</v>
+        <v>18510</v>
       </c>
       <c r="N19" t="n">
         <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>70945285955</v>
+        <v>73902496360</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2183,10 +2183,10 @@
         <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-480000</v>
+        <v>-531000</v>
       </c>
       <c r="S19" t="n">
-        <v>-158000</v>
+        <v>-246000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13800</v>
+        <v>13670</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-6.19%</t>
+          <t>-7.07%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
         <v>15420</v>
       </c>
       <c r="M20" t="n">
-        <v>13700</v>
+        <v>13650</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>29561514020</v>
+        <v>30612835525</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2275,7 +2275,7 @@
         <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-60000</v>
+        <v>-57000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11240</v>
+        <v>11120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-9.72%</t>
+          <t>-10.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
         <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2352,13 +2352,13 @@
         <v>13900</v>
       </c>
       <c r="M21" t="n">
-        <v>11240</v>
+        <v>11100</v>
       </c>
       <c r="N21" t="n">
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>65162138690</v>
+        <v>66460265885</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2367,7 +2367,7 @@
         <v>465</v>
       </c>
       <c r="R21" t="n">
-        <v>-140000</v>
+        <v>-191000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260914_14.xlsx
+++ b/data/trending_integrated_20260914_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F2" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>270513367245</v>
+        <v>270622742745</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신 대장주로서의 기대감과 3연상 가능성에 대한 언급. 일부에서는 시세 끝 조심 및 급락 가능성 언급.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 급등 기대감. 프로그램 매수세 유입 및 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '3연상', '주포']</t>
+          <t>['광반도체', '광통신', '3연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9820</v>
+        <v>6680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.15%</t>
+          <t>+21.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.55</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7910</v>
+        <v>5510</v>
       </c>
       <c r="K3" t="n">
-        <v>7800</v>
+        <v>5910</v>
       </c>
       <c r="L3" t="n">
-        <v>9880</v>
+        <v>7160</v>
       </c>
       <c r="M3" t="n">
-        <v>7540</v>
+        <v>5890</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>103935841395</v>
+        <v>60005919675</v>
       </c>
       <c r="P3" t="n">
-        <v>25050</v>
+        <v>10360</v>
       </c>
       <c r="Q3" t="n">
-        <v>3705</v>
+        <v>2965</v>
       </c>
       <c r="R3" t="n">
-        <v>33000</v>
+        <v>-66000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
+          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['펩타이드', '특허 등록', '면역 조절']</t>
+          <t>['AI 보안', '딥페이크', '단기 급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6660</v>
+        <v>9230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.87%</t>
+          <t>+16.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="H4" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5510</v>
+        <v>7910</v>
       </c>
       <c r="K4" t="n">
-        <v>5910</v>
+        <v>7800</v>
       </c>
       <c r="L4" t="n">
-        <v>7160</v>
+        <v>9880</v>
       </c>
       <c r="M4" t="n">
-        <v>5890</v>
+        <v>7540</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>58591942780</v>
+        <v>112824545250</v>
       </c>
       <c r="P4" t="n">
-        <v>10360</v>
+        <v>25050</v>
       </c>
       <c r="Q4" t="n">
-        <v>2965</v>
+        <v>3705</v>
       </c>
       <c r="R4" t="n">
-        <v>-66000</v>
+        <v>33000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '딥페이크', '단기 급등']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
         <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>38577669085</v>
+        <v>38923141280</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9160</v>
+        <v>4245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.49%</t>
+          <t>+9.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="G6" t="n">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8290</v>
+        <v>3870</v>
       </c>
       <c r="K6" t="n">
-        <v>8300</v>
+        <v>3860</v>
       </c>
       <c r="L6" t="n">
-        <v>9440</v>
+        <v>4620</v>
       </c>
       <c r="M6" t="n">
-        <v>8300</v>
+        <v>3740</v>
       </c>
       <c r="N6" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>43585131640</v>
+        <v>296482985910</v>
       </c>
       <c r="P6" t="n">
-        <v>12800</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>5340</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>568000</v>
+        <v>-202000</v>
       </c>
       <c r="S6" t="n">
-        <v>104000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
+          <t>6G 시대 개막에 따른 수혜 기대감. 국책사업 선정 및 기술력 기반으로 높은 상승 잠재력 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['폴더블', '매출 증', '전환사채']</t>
+          <t>['6G', '국책사업', '기술력']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4250</v>
+        <v>9090</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.82%</t>
+          <t>+9.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.45</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>293</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3870</v>
+        <v>8290</v>
       </c>
       <c r="K7" t="n">
-        <v>3860</v>
+        <v>8300</v>
       </c>
       <c r="L7" t="n">
-        <v>4620</v>
+        <v>9440</v>
       </c>
       <c r="M7" t="n">
-        <v>3740</v>
+        <v>8300</v>
       </c>
       <c r="N7" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>293646813872</v>
+        <v>43944468200</v>
       </c>
       <c r="P7" t="n">
-        <v>8100</v>
+        <v>12800</v>
       </c>
       <c r="Q7" t="n">
-        <v>592</v>
+        <v>5340</v>
       </c>
       <c r="R7" t="n">
-        <v>-202000</v>
+        <v>568000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6G 시대 개막 및 국책사업 선정 가능성에 따른 8000원 이상 목표가 제시. 투자 경고 및 변동성 언급.</t>
+          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['6G', '국책사업', '투자경고']</t>
+          <t>['폴더블', '매출 증', '전환사채']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>441270</t>
         </is>
       </c>
     </row>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2805</v>
+        <v>2815</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>+7.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
         <v>229</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>101821482105</v>
+        <v>102212820374</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16880</v>
+        <v>16890</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.11%</t>
+          <t>+5.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>262229708020</v>
+        <v>263063835300</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론과 보안주로서의 역할에 대한 기대감. 2연상 가능성 언급 및 매도세에 대한 불만 표현.</t>
+          <t>AI 개발 속도 조절론과 맞물려 보안주 부각. 단기 급등 후 조정 구간 진입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '2연상']</t>
+          <t>['AI', '보안주', '급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22250</v>
+        <v>22200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.97%</t>
+          <t>+3.74%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="H10" t="n">
         <v>28.81</v>
@@ -1346,7 +1346,7 @@
         <v>28.89</v>
       </c>
       <c r="O10" t="n">
-        <v>77146905175</v>
+        <v>80933657300</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 수주 성공 및 1.6조 원 규모 실적 돌파, 증권사 목표가 상향 등 긍정적 요인에 기반한 상승 전망.</t>
+          <t>대형 상선 수주 공시 기반으로 목표 주가 상향 전망. 조선업 호황 및 숏커버 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', 'LNG선', '실적']</t>
+          <t>['수주', '조선업', '목표주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8560</v>
+        <v>8590</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.26%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G11" t="n">
-        <v>1378</v>
+        <v>1504</v>
       </c>
       <c r="H11" t="n">
         <v>0.75</v>
@@ -1438,7 +1438,7 @@
         <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>32004687535</v>
+        <v>32439263080</v>
       </c>
       <c r="P11" t="n">
         <v>21500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>항암 신약 임상 결과 발표 및 글로벌 심포지엄 개최 등 핵폭탄급 재료 기반 상승 기대. 낮은 시가총액으로 인한 큰 폭 상승 전망.</t>
+          <t>암 치료 바이오 신약 관련 심포지엄 발표 임박. 핵폭탄급 재료와 낮은 시총으로 인한 급등 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['항암', '신약', '심포지엄']</t>
+          <t>['바이오신약', '심포지엄', '임상결과']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15000</v>
+        <v>14910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-1.97</v>
       </c>
       <c r="E12" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="F12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G12" t="n">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="H12" t="n">
         <v>1.17</v>
@@ -1530,7 +1530,7 @@
         <v>3.14</v>
       </c>
       <c r="O12" t="n">
-        <v>108691448605</v>
+        <v>120197215250</v>
       </c>
       <c r="P12" t="n">
         <v>36200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>이란-걸프국 회담 연기 및 국제유가 폭등 관련 수혜 기대감. 단기 급등락 반복.</t>
+          <t>중동 지정학적 리스크 및 국제 유가 급등에 따른 수혜 기대. 회담 연기 및 폭발음 관련 뉴스 주목.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['국제유가', '호르무즈', '지정학']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14390</v>
+        <v>14400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F13" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G13" t="n">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="H13" t="n">
         <v>1.88</v>
@@ -1622,7 +1622,7 @@
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>168214182280</v>
+        <v>169911696440</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 성장 및 15000원 돌파 기대감. 대장주로서의 역할 수행 미흡에 대한 아쉬움 표현.</t>
+          <t>AIDC 광통신 기술력 기반으로 한 상승 전망. GPU 확보와 연결되는 HBM 투자 확대 수혜 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', '대장주']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1856</v>
+        <v>1852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>16342265201</v>
+        <v>16742955960</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>249750</v>
+        <v>249500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.76%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G15" t="n">
-        <v>1769</v>
+        <v>1712</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3132141379750</v>
+        <v>3307522141000</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 속도 조절론, 정치적 이슈와 연계된 부정적 전망 및 투자자 불만 토로.</t>
+          <t>AI 속도 조절론 및 정치적 이슈로 인한 투자 심리 악화. 국장 전반에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '금산법', '실적']</t>
+          <t>['AI', '국장', '이재명']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86300</v>
+        <v>86700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F16" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
-        <v>828</v>
+        <v>863</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1892,13 +1892,13 @@
         <v>90400</v>
       </c>
       <c r="M16" t="n">
-        <v>86300</v>
+        <v>86100</v>
       </c>
       <c r="N16" t="n">
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>199442286200</v>
+        <v>211083116400</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>우상향 추세 및 급등 구간 진입 기대감과 함께, 국제 유가 상승 시 원전주 상승 가능성 언급.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 공매도 세력에 대한 경계와 함께 상승 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '원전주', '공매']</t>
+          <t>['국제유가', '원전주', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11560</v>
+        <v>11610</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.94%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
         <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H17" t="n">
         <v>0.22</v>
@@ -1984,13 +1984,13 @@
         <v>13230</v>
       </c>
       <c r="M17" t="n">
-        <v>11550</v>
+        <v>11490</v>
       </c>
       <c r="N17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>58449553075</v>
+        <v>59016703335</v>
       </c>
       <c r="P17" t="n">
         <v>20850</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1701000</v>
+        <v>1698000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-6.13%</t>
+          <t>-6.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="G18" t="n">
-        <v>1855</v>
+        <v>1847</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4873211088000</v>
+        <v>5103826622500</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>하락세에 대한 불만과 정치적 언급이 혼재. 연말 300 목표가 및 외국인 선물 매수 전환 등 일부 긍정적 요소 언급.</t>
+          <t>정치적 이슈와 외풍에 따른 증시 불안정성 속 급락세. 투자 심리 위축 및 하락 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['미국금리', '외국인', 'AI']</t>
+          <t>['AI', '증시', '하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18520</v>
+        <v>18620</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.89%</t>
+          <t>-6.39%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="H19" t="n">
         <v>10.55</v>
@@ -2168,13 +2168,13 @@
         <v>19550</v>
       </c>
       <c r="M19" t="n">
-        <v>18510</v>
+        <v>18500</v>
       </c>
       <c r="N19" t="n">
         <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>73902496360</v>
+        <v>75829790935</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13670</v>
+        <v>13680</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.07%</t>
+          <t>-7.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
         <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
         <v>15420</v>
       </c>
       <c r="M20" t="n">
-        <v>13650</v>
+        <v>13590</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>30612835525</v>
+        <v>31372795360</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2326,13 +2326,13 @@
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G21" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2352,13 +2352,13 @@
         <v>13900</v>
       </c>
       <c r="M21" t="n">
-        <v>11100</v>
+        <v>11050</v>
       </c>
       <c r="N21" t="n">
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>66460265885</v>
+        <v>67334511425</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>

--- a/data/trending_integrated_20260914_14.xlsx
+++ b/data/trending_integrated_20260914_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.28</v>
       </c>
       <c r="E2" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>270622742745</v>
+        <v>270712738755</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6680</v>
+        <v>7050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.23%</t>
+          <t>+27.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>60005919675</v>
+        <v>65201642875</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9230</v>
+        <v>9220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.69%</t>
+          <t>+16.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>112824545250</v>
+        <v>116669370570</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2875</v>
+        <v>2890</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.22%</t>
+          <t>+11.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>38923141280</v>
+        <v>39160086420</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4245</v>
+        <v>4255</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.69%</t>
+          <t>+9.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G6" t="n">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>296482985910</v>
+        <v>298622681317</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6G 시대 개막에 따른 수혜 기대감. 국책사업 선정 및 기술력 기반으로 높은 상승 잠재력 언급.</t>
+          <t>6G 시대 기대감 및 국책사업 선정 관련 긍정적 전망, 단기 급등 및 재료 기반 상승 가능성 시사.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['6G', '국책사업', '기술력']</t>
+          <t>['6G', '국책사업', '급등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9090</v>
+        <v>9100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.65%</t>
+          <t>+9.77%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>43944468200</v>
+        <v>44196109150</v>
       </c>
       <c r="P7" t="n">
         <v>12800</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2815</v>
+        <v>2805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.44%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
         <v>229</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>102212820374</v>
+        <v>102885193938</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16890</v>
+        <v>17040</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.17%</t>
+          <t>+6.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F9" t="n">
         <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>263063835300</v>
+        <v>265344219990</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론과 맞물려 보안주 부각. 단기 급등 후 조정 구간 진입.</t>
+          <t>AI 개발 속도 조절론에 따른 변동성 확대 및 주가 하락, 보안주로서의 방어 기대감과 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '급등']</t>
+          <t>['AI', '보안주', '하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22200</v>
+        <v>8670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.74%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>-0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>261</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="G10" t="n">
-        <v>446</v>
+        <v>1618</v>
       </c>
       <c r="H10" t="n">
-        <v>28.81</v>
+        <v>0.75</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21400</v>
+        <v>8290</v>
       </c>
       <c r="K10" t="n">
-        <v>21100</v>
+        <v>8100</v>
       </c>
       <c r="L10" t="n">
-        <v>22500</v>
+        <v>9050</v>
       </c>
       <c r="M10" t="n">
-        <v>20850</v>
+        <v>8060</v>
       </c>
       <c r="N10" t="n">
-        <v>28.89</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>80933657300</v>
+        <v>35112524285</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>21500</v>
       </c>
       <c r="Q10" t="n">
-        <v>18440</v>
+        <v>2300</v>
       </c>
       <c r="R10" t="n">
-        <v>688000</v>
+        <v>-27000</v>
       </c>
       <c r="S10" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대형 상선 수주 공시 기반으로 목표 주가 상향 전망. 조선업 호황 및 숏커버 기대감.</t>
+          <t>신약 개발 관련 빅이슈 및 임상 결과 발표에 대한 높은 기대감, 시총 대비 강력한 재료 기반의 급등 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', '조선업', '목표주가']</t>
+          <t>['신약', '임상', '재료']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8590</v>
+        <v>22150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.62%</t>
+          <t>+3.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.54</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>243</v>
+        <v>133</v>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>1504</v>
+        <v>475</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>28.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8290</v>
+        <v>21400</v>
       </c>
       <c r="K11" t="n">
-        <v>8100</v>
+        <v>21100</v>
       </c>
       <c r="L11" t="n">
-        <v>9050</v>
+        <v>22500</v>
       </c>
       <c r="M11" t="n">
-        <v>8060</v>
+        <v>20850</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>28.89</v>
       </c>
       <c r="O11" t="n">
-        <v>32439263080</v>
+        <v>83960809975</v>
       </c>
       <c r="P11" t="n">
-        <v>21500</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>2300</v>
+        <v>18440</v>
       </c>
       <c r="R11" t="n">
-        <v>-27000</v>
+        <v>688000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>암 치료 바이오 신약 관련 심포지엄 발표 임박. 핵폭탄급 재료와 낮은 시총으로 인한 급등 기대감.</t>
+          <t>대규모 수주 소식 및 증권사 목표가 상향에 따른 긍정적 전망, 숏커버 기대감 상승.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['바이오신약', '심포지엄', '임상결과']</t>
+          <t>['수주', '전망', '숏커버']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14910</v>
+        <v>14400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.97</v>
+        <v>-0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>317</v>
+        <v>220</v>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="G12" t="n">
-        <v>809</v>
+        <v>838</v>
       </c>
       <c r="H12" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14610</v>
+        <v>14150</v>
       </c>
       <c r="K12" t="n">
-        <v>15420</v>
+        <v>13850</v>
       </c>
       <c r="L12" t="n">
-        <v>16510</v>
+        <v>14950</v>
       </c>
       <c r="M12" t="n">
-        <v>14320</v>
+        <v>13800</v>
       </c>
       <c r="N12" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>120197215250</v>
+        <v>171151685655</v>
       </c>
       <c r="P12" t="n">
-        <v>36200</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>8920</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-83000</v>
+        <v>-325000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>중동 지정학적 리스크 및 국제 유가 급등에 따른 수혜 기대. 회담 연기 및 폭발음 관련 뉴스 주목.</t>
+          <t>AIDC 광통신 기술력에 대한 긍정적 전망, GPU 확보 및 연결성 강화에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '지정학']</t>
+          <t>['광통신', 'AIDC', 'GPU']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14400</v>
+        <v>14850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>212</v>
+        <v>330</v>
       </c>
       <c r="F13" t="n">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="G13" t="n">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="H13" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K13" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L13" t="n">
-        <v>14950</v>
+        <v>16510</v>
       </c>
       <c r="M13" t="n">
-        <v>13800</v>
+        <v>14320</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>169911696440</v>
+        <v>122131640330</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R13" t="n">
-        <v>-325000</v>
+        <v>-83000</v>
       </c>
       <c r="S13" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술력 기반으로 한 상승 전망. GPU 확보와 연결되는 HBM 투자 확대 수혜 기대.</t>
+          <t>중동 지정학적 리스크 및 국제 유가 급등에 따른 수혜 기대. 회담 연기 및 폭발음 관련 뉴스 주목.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['국제유가', '호르무즈', '지정학']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>16742955960</v>
+        <v>16869713935</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>249500</v>
+        <v>249250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-3.95%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="G15" t="n">
-        <v>1712</v>
+        <v>1707</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3307522141000</v>
+        <v>3425045117500</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 속도 조절론 및 정치적 이슈로 인한 투자 심리 악화. 국장 전반에 대한 부정적 전망.</t>
+          <t>정치적 이슈로 인한 주가 영향 및 투자자들의 불신, 탈출 심리가 강하게 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '국장', '이재명']</t>
+          <t>['정치', '불신', '탈출']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86700</v>
+        <v>87000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-4.19%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>141</v>
       </c>
       <c r="G16" t="n">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1898,7 +1898,7 @@
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>211083116400</v>
+        <v>217382887150</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 공매도 세력에 대한 경계와 함께 상승 기대감.</t>
+          <t>주가 등락에 대한 혼조세, 외인·기관 매도에 따른 불확실성 및 투자자들의 불만 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '원전주', '공매도']</t>
+          <t>['등락', '매도', '불만']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11610</v>
+        <v>11560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
         <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H17" t="n">
         <v>0.22</v>
@@ -1990,7 +1990,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>59016703335</v>
+        <v>59258711055</v>
       </c>
       <c r="P17" t="n">
         <v>20850</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1698000</v>
+        <v>1704000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-6.29%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G18" t="n">
-        <v>1847</v>
+        <v>1824</v>
       </c>
       <c r="H18" t="n">
         <v>50.47</v>
@@ -2082,7 +2082,7 @@
         <v>50.55</v>
       </c>
       <c r="O18" t="n">
-        <v>5103826622500</v>
+        <v>5241333487500</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 이슈와 외풍에 따른 증시 불안정성 속 급락세. 투자 심리 위축 및 하락 전망.</t>
+          <t>정치적 요인과 거시 경제 불안으로 인한 주가 하락, 투자자들의 절망감과 투매 심리가 두드러짐.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI', '증시', '하락']</t>
+          <t>['정치', '하락', '절망']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18620</v>
+        <v>18640</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.39%</t>
+          <t>-6.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="H19" t="n">
         <v>10.55</v>
@@ -2174,7 +2174,7 @@
         <v>10.65</v>
       </c>
       <c r="O19" t="n">
-        <v>75829790935</v>
+        <v>77205200485</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13680</v>
+        <v>13650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.00%</t>
+          <t>-7.21%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>31372795360</v>
+        <v>31800220250</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11120</v>
+        <v>11130</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.68%</t>
+          <t>-10.60%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F21" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>67334511425</v>
+        <v>67775565845</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>단타 및 급등주 흐름, 외인 대량 매수 중이라는 언급. 투자 경고 및 주의 필요성 시사.</t>
+          <t>주가 급락 및 투자자들의 큰 손실, 종목에 대한 강한 부정적 감정과 이탈 심리가 관찰됨.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['단타', '외인매수', '투자경고']</t>
+          <t>['급락', '손실', '이탈']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">

--- a/data/trending_integrated_20260914_14.xlsx
+++ b/data/trending_integrated_20260914_14.xlsx
@@ -584,7 +584,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H2" t="n">
         <v>17.67</v>
@@ -610,7 +610,7 @@
         <v>17.95</v>
       </c>
       <c r="O2" t="n">
-        <v>270712738755</v>
+        <v>270844461775</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7050</v>
+        <v>7160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.95%</t>
+          <t>+29.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
@@ -702,7 +702,7 @@
         <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>65201642875</v>
+        <v>68398563735</v>
       </c>
       <c r="P3" t="n">
         <v>10360</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9220</v>
+        <v>9020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+16.56%</t>
+          <t>+14.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>116669370570</v>
+        <v>118747340770</v>
       </c>
       <c r="P4" t="n">
         <v>25050</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2890</v>
+        <v>2915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+11.80%</t>
+          <t>+12.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
         <v>106</v>
@@ -886,7 +886,7 @@
         <v>3.64</v>
       </c>
       <c r="O5" t="n">
-        <v>39160086420</v>
+        <v>39329839185</v>
       </c>
       <c r="P5" t="n">
         <v>6180</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4255</v>
+        <v>4290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>+10.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.45</v>
       </c>
       <c r="E6" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H6" t="n">
         <v>0.59</v>
@@ -978,7 +978,7 @@
         <v>1.04</v>
       </c>
       <c r="O6" t="n">
-        <v>298622681317</v>
+        <v>300433163235</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6G 시대 기대감 및 국책사업 선정 관련 긍정적 전망, 단기 급등 및 재료 기반 상승 가능성 시사.</t>
+          <t>6G 시대 개막 및 국책사업 선정 가능성에 따른 기대감 표출.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['6G', '국책사업', '급등']</t>
+          <t>['6G', '국책사업', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9100</v>
+        <v>9040</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.77%</t>
+          <t>+9.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.82</v>
       </c>
       <c r="O7" t="n">
-        <v>44196109150</v>
+        <v>45039239970</v>
       </c>
       <c r="P7" t="n">
         <v>12800</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2805</v>
+        <v>2815</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>+7.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-2.39</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
         <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H8" t="n">
         <v>1.44</v>
@@ -1162,7 +1162,7 @@
         <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>102885193938</v>
+        <v>103766543401</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17040</v>
+        <v>17220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.10%</t>
+          <t>+7.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H9" t="n">
         <v>2.7</v>
@@ -1254,7 +1254,7 @@
         <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>265344219990</v>
+        <v>273314394805</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 변동성 확대 및 주가 하락, 보안주로서의 방어 기대감과 투자 심리 위축.</t>
+          <t>AI 개발 속도 조절론과 관련하여 보안주의 부각 가능성 언급 및 주가 변동성 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '보안주', '하락']</t>
+          <t>['AI', '보안주', '변동성']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8670</v>
+        <v>8880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+7.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="F10" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G10" t="n">
-        <v>1618</v>
+        <v>1715</v>
       </c>
       <c r="H10" t="n">
         <v>0.75</v>
@@ -1337,7 +1337,7 @@
         <v>8100</v>
       </c>
       <c r="L10" t="n">
-        <v>9050</v>
+        <v>9240</v>
       </c>
       <c r="M10" t="n">
         <v>8060</v>
@@ -1346,7 +1346,7 @@
         <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>35112524285</v>
+        <v>42686596125</v>
       </c>
       <c r="P10" t="n">
         <v>21500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>신약 개발 관련 빅이슈 및 임상 결과 발표에 대한 높은 기대감, 시총 대비 강력한 재료 기반의 급등 전망.</t>
+          <t>임상 결과 발표 임박 및 글로벌 제약사 멘토십 기반 신약 개발 기대감 고조.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['신약', '임상', '재료']</t>
+          <t>['신약개발', '임상결과', '기대감']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22150</v>
+        <v>22000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+2.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="H11" t="n">
         <v>28.81</v>
@@ -1438,7 +1438,7 @@
         <v>28.89</v>
       </c>
       <c r="O11" t="n">
-        <v>83960809975</v>
+        <v>86747835450</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대규모 수주 소식 및 증권사 목표가 상향에 따른 긍정적 전망, 숏커버 기대감 상승.</t>
+          <t>대형 수주 공시 확인 및 숏커버, 목표주가 상향 등 긍정적 뉴스 기반 분석.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '전망', '숏커버']</t>
+          <t>['수주', '숏커버', '목표주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14400</v>
+        <v>14430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F12" t="n">
         <v>125</v>
       </c>
       <c r="G12" t="n">
-        <v>838</v>
+        <v>874</v>
       </c>
       <c r="H12" t="n">
         <v>1.88</v>
@@ -1530,7 +1530,7 @@
         <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>171151685655</v>
+        <v>172352828005</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술력에 대한 긍정적 전망, GPU 확보 및 연결성 강화에 따른 주가 상승 기대감.</t>
+          <t>AIDC 광통신 기술 발전 뉴스와 함께 향후 주가 상승에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['광통신', 'AIDC', '기술력']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14850</v>
+        <v>14800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.64%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.97</v>
       </c>
       <c r="E13" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F13" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G13" t="n">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="H13" t="n">
         <v>1.17</v>
@@ -1622,7 +1622,7 @@
         <v>3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>122131640330</v>
+        <v>123090655540</v>
       </c>
       <c r="P13" t="n">
         <v>36200</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1851</v>
+        <v>1842</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -1708,13 +1708,13 @@
         <v>1961</v>
       </c>
       <c r="M14" t="n">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="N14" t="n">
         <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>16869713935</v>
+        <v>17243508438</v>
       </c>
       <c r="P14" t="n">
         <v>4795</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>249250</v>
+        <v>249000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G15" t="n">
-        <v>1707</v>
+        <v>1719</v>
       </c>
       <c r="H15" t="n">
         <v>46.64</v>
@@ -1806,7 +1806,7 @@
         <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3425045117500</v>
+        <v>3534080836500</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 주가 영향 및 투자자들의 불신, 탈출 심리가 강하게 나타남.</t>
+          <t>정치적 이슈와 더불어 주가 반등 요인 부재, 개인 투자자들의 투자 심리 악화가 복합적으로 작용.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '불신', '탈출']</t>
+          <t>['정치', '투자심리', '주가']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87000</v>
+        <v>86900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>-4.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G16" t="n">
-        <v>878</v>
+        <v>892</v>
       </c>
       <c r="H16" t="n">
         <v>23.56</v>
@@ -1898,7 +1898,7 @@
         <v>23.59</v>
       </c>
       <c r="O16" t="n">
-        <v>217382887150</v>
+        <v>221677813950</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 등락에 대한 혼조세, 외인·기관 매도에 따른 불확실성 및 투자자들의 불만 표출.</t>
+          <t>장기적 상승 가능성 언급과 함께 정부 정책 및 시장 분위기에 대한 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['등락', '매도', '불만']</t>
+          <t>['상승가능성', '정부정책', '시장']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11560</v>
+        <v>11580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.94%</t>
+          <t>-5.78%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.72</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
         <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H17" t="n">
         <v>0.22</v>
@@ -1984,13 +1984,13 @@
         <v>13230</v>
       </c>
       <c r="M17" t="n">
-        <v>11490</v>
+        <v>11470</v>
       </c>
       <c r="N17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>59258711055</v>
+        <v>59797700170</v>
       </c>
       <c r="P17" t="n">
         <v>20850</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1704000</v>
+        <v>18640</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>-6.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>466</v>
+        <v>69</v>
       </c>
       <c r="G18" t="n">
-        <v>1824</v>
+        <v>502</v>
       </c>
       <c r="H18" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K18" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L18" t="n">
-        <v>1740000</v>
+        <v>19550</v>
       </c>
       <c r="M18" t="n">
-        <v>1695000</v>
+        <v>18500</v>
       </c>
       <c r="N18" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O18" t="n">
-        <v>5241333487500</v>
+        <v>78532500805</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-1117000</v>
+        <v>-531000</v>
       </c>
       <c r="S18" t="n">
-        <v>-203000</v>
+        <v>-246000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 요인과 거시 경제 불안으로 인한 주가 하락, 투자자들의 절망감과 투매 심리가 두드러짐.</t>
+          <t>대차해지 운동을 통한 공매도 세력 견제 및 주가 부양 의지를 보이는 게시글 다수.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정치', '하락', '절망']</t>
+          <t>['대차해지', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18640</v>
+        <v>1697000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-6.28%</t>
+          <t>-6.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>116</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>474</v>
       </c>
       <c r="G19" t="n">
-        <v>491</v>
+        <v>1836</v>
       </c>
       <c r="H19" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K19" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L19" t="n">
-        <v>19550</v>
+        <v>1740000</v>
       </c>
       <c r="M19" t="n">
-        <v>18500</v>
+        <v>1695000</v>
       </c>
       <c r="N19" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O19" t="n">
-        <v>77205200485</v>
+        <v>5389968049500</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R19" t="n">
-        <v>-531000</v>
+        <v>-1117000</v>
       </c>
       <c r="S19" t="n">
-        <v>-246000</v>
+        <v>-203000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대차해지 운동 동참 권유 및 공매도 작살 가능성 언급. 저점이 높아지고 있으며, 침착한 기다림이 필요하다는 의견.</t>
+          <t>현 정부 정책 및 시장 상황에 대한 부정적 인식, 향후 주가 하락에 대한 우려가 지배적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,20 +2199,20 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주주운동']</t>
+          <t>['정부정책', '시장상황', '주가하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>31800220250</v>
+        <v>32132454400</v>
       </c>
       <c r="P20" t="n">
         <v>19380</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11130</v>
+        <v>11120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.60%</t>
+          <t>-10.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H21" t="n">
         <v>17.58</v>
@@ -2358,7 +2358,7 @@
         <v>17.07</v>
       </c>
       <c r="O21" t="n">
-        <v>67775565845</v>
+        <v>68167799685</v>
       </c>
       <c r="P21" t="n">
         <v>14350</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
